--- a/enrollment/050_win_free_days_of_enrollment_contest_entry--enrollment.xlsx
+++ b/enrollment/050_win_free_days_of_enrollment_contest_entry--enrollment.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,38 +520,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>contest_entry</t>
+          <t>school_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Contest Entry</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your school name?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>School name is required</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>additional_information</t>
+          <t>school_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Additional Information</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What type of school do you attend?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select your school type</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -561,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>school_name</t>
+          <t>age_range</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>School Name</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is your age range?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Age range is required</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>school_type</t>
+          <t>gender</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>School Type</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is your gender?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please select your gender</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>age_range</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Age Range</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is your phone number?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phone number is required</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gender</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is your email address?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Email address is required</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -658,17 +682,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>What is your address?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Enter phone number</t>
+          <t>Address is required</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -685,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Do you want to provide additional information?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Yes/No</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -708,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>school_name_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Address</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is the name of your school (again)?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>School name is required</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -726,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>school_type_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What type of school do you attend (again)?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please select your school type</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -749,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>school_name_2</t>
+          <t>age_range_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>School Name</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is your age range (again)?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Age range is required</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -777,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>school_type_2</t>
+          <t>gender_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>School Type</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is your gender (again)?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please select your gender</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -795,20 +839,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>age_range_2</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Age Range</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>What is your phone number (again)?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Phone number is required</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>yes</t>
@@ -818,20 +866,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gender_2</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gender</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>What is your email address (again)?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Email address is required</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>yes</t>
@@ -846,396 +898,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>phone_2</t>
+          <t>address_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phone 2</t>
+          <t>What is your address (again)?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Enter phone number 2</t>
+          <t>Address is required</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>email_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>address_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Address 2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>school_name_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>School Name</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>school_type_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>School Type</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>age_range_3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Age Range</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>gender_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Gender</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>phone_2_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Phone 2</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Enter phone number 2</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>email_2_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>address_2_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Address 2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>school_name_4</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>School Name</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>school_type_4</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>School Type</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>age_range_4</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Age Range</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>gender_4</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Gender</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>phone_2_4</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Phone 2</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Enter phone number 2</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>email_4</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>address_4</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Address 4</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1252,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1612,346 +1288,6 @@
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>school_type_3_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>high_school</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>High School</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>school_type_3_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>middle_school</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Middle School</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>school_type_3_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>age_range_3_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>10-13</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>age_range_3_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>14-17</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>14-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>age_range_3_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>18-24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>18-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>age_range_3_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>25_or_older</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>25 or older</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>gender_3_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>gender_3_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>gender_3_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>school_type_4_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>high_school</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>High School</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>school_type_4_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>middle_school</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Middle School</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>school_type_4_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>age_range_4_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>10-13</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>10-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>age_range_4_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>14-17</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>14-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>age_range_4_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>18-24</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>18-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>age_range_4_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>25_or_older</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>25 or older</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>gender_4_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>gender_4_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>gender_4_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
